--- a/tables/Skill.xlsx
+++ b/tables/Skill.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.25" customWidth="1" min="1" max="1"/>
@@ -586,11 +586,6 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>Note</t>
         </is>
       </c>
@@ -627,11 +622,6 @@
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>장부방에서 해금, 결박 문·사슬 끊기</t>
         </is>

--- a/tables/Skill.xlsx
+++ b/tables/Skill.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>스킬 공격·쿨타임·해금 방식·효과.</t>
+          <t>CSV,스킬 공격·쿨타임·해금 방식·효과.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>

--- a/tables/Skill.xlsx
+++ b/tables/Skill.xlsx
@@ -603,7 +603,7 @@
         <v>30010</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>5006</v>

--- a/tables/Skill.xlsx
+++ b/tables/Skill.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.25" customWidth="1" min="1" max="1"/>
@@ -450,7 +450,9 @@
     <col width="8.25" customWidth="1" min="5" max="5"/>
     <col width="12.25" customWidth="1" min="6" max="6"/>
     <col width="8.380000000000001" customWidth="1" min="7" max="7"/>
-    <col width="30.38" customWidth="1" min="8" max="8"/>
+    <col width="12.25" customWidth="1" min="8" max="8"/>
+    <col width="8.380000000000001" customWidth="1" min="9" max="9"/>
+    <col width="30.38" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -461,7 +463,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>한 행 = 스킬 하나. MP 없음, Cooldown(ms)만. WeaponID는 Weapon ID, AttackID는 Attack ID.</t>
+          <t>한 행 = 스킬 하나. MP 없음, Cooldown(ms)만. WeaponID는 Item ID, StateID는 State ID. DamageMult는 만분율(10000 = ATK 그대로), PoiseDamage는 체세 피해. 스킬 공격은 회피 불가(옛 Attack 5006 값을 옮김, 10/29).</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -566,25 +568,35 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>AttackID</t>
+          <t>StateID</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>DamageMult</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>PoiseDamage</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>Cooldown</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>UnlockType</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Effect</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -606,22 +618,28 @@
         <v>6002</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5006</v>
+        <v>10009</v>
       </c>
       <c r="F7" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>8000</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>ROOM_LEDGER</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>CUT_BIND</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>장부방에서 해금, 결박 문·사슬 끊기</t>
         </is>

--- a/tables/Skill.xlsx
+++ b/tables/Skill.xlsx
@@ -435,217 +435,227 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.25" customWidth="1" min="1" max="1"/>
-    <col width="7.88" customWidth="1" min="2" max="2"/>
-    <col width="8.380000000000001" customWidth="1" min="3" max="3"/>
-    <col width="9.380000000000001" customWidth="1" min="4" max="4"/>
-    <col width="8.25" customWidth="1" min="5" max="5"/>
-    <col width="12.25" customWidth="1" min="6" max="6"/>
-    <col width="8.380000000000001" customWidth="1" min="7" max="7"/>
-    <col width="12.25" customWidth="1" min="8" max="8"/>
-    <col width="8.380000000000001" customWidth="1" min="9" max="9"/>
-    <col width="30.38" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>규칙</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>한 행 = 스킬 하나. MP 없음, Cooldown(ms)만. WeaponID는 Item ID, StateID는 State ID. DamageMult는 만분율(10000 = ATK 그대로), PoiseDamage는 체세 피해. 스킬 공격은 회피 불가(옛 Attack 5006 값을 옮김, 10/29).</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>CSV,스킬 공격·쿨타임·해금 방식·효과.</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>역할</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>스킬 입력과 해금 처리가 읽는다.</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>의도</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>무기마다 스킬을 붙이기 위해.</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Name, Note</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
-      <c r="H5" s="1" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>TextID</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>WeaponID</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>StateID</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>DamageMult</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>PoiseDamage</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>UnlockType</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Effect</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>7001</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>결박 가르기</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>30010</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>6002</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>10009</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>8000</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>ROOM_LEDGER</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>CUT_BIND</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>장부방에서 해금, 결박 문·사슬 끊기</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetPr>
+    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
+    <ns0:pageSetUpPr/>
+  </ns0:sheetPr>
+  <ns0:dimension ref="A1:K7"/>
+  <ns0:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <ns0:cols>
+    <ns0:col width="7.25" customWidth="1" min="1" max="1"/>
+    <ns0:col width="7.88" customWidth="1" min="2" max="2"/>
+    <ns0:col width="8.380000000000001" customWidth="1" min="3" max="3"/>
+    <ns0:col width="9.380000000000001" customWidth="1" min="4" max="4"/>
+    <ns0:col width="8.25" customWidth="1" min="5" max="5"/>
+    <ns0:col width="12.25" customWidth="1" min="6" max="6"/>
+    <ns0:col width="8.380000000000001" customWidth="1" min="7" max="7"/>
+    <ns0:col width="12.25" customWidth="1" min="8" max="8"/>
+    <ns0:col width="8.380000000000001" customWidth="1" min="9" max="9"/>
+    <ns0:col width="30.38" customWidth="1" min="10" max="10"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1">
+      <ns0:c r="A1" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>규칙</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B1" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">한 행 = 스킬 하나. MP 없음, Cooldown(ms)만. WeaponID는 Item ID, StateID는 State ID. DamageMult는 만분율(10000 = ATK 그대로), PoiseDamage는 체세 피해. 스킬 공격은 회피 불가(옛 Attack 5006 값을 옮김, 10/29).
+[추출 지정 규칙]
+@column Name=TextID;Type=Integer;Minimum=1;ReferenceTable=Language
+@column Name=WeaponID;Type=Integer;Minimum=1;ReferenceTable=Item
+@column Name=StateID;Type=Integer;Minimum=0;ReferenceTable=State
+@column Name=DamageMult;Type=Integer;Minimum=0;Unit=per_10000
+@column Name=PoiseDamage;Type=Integer;Minimum=0
+@column Name=Cooldown;Type=Integer;Minimum=0;Unit=ms
+@column Name=UnlockType;Type=Text;AllowedValues=ROOM_LEDGER
+@column Name=Effect;Type=Text;AllowedValues=CUT_BIND
+@check Kind=ReferenceValue;Column=WeaponID;Table=Item;TargetColumn=ItemType;Value=Weapon;Code=ITEM_TYPE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C1" s="1" t="n"/>
+      <ns0:c r="D1" s="1" t="n"/>
+      <ns0:c r="E1" s="1" t="n"/>
+      <ns0:c r="F1" s="1" t="n"/>
+      <ns0:c r="G1" s="1" t="n"/>
+      <ns0:c r="H1" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="2">
+      <ns0:c r="A2" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>기능</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B2" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CSV,스킬 공격·쿨타임·해금 방식·효과.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C2" s="1" t="n"/>
+      <ns0:c r="D2" s="1" t="n"/>
+      <ns0:c r="E2" s="1" t="n"/>
+      <ns0:c r="F2" s="1" t="n"/>
+      <ns0:c r="G2" s="1" t="n"/>
+      <ns0:c r="H2" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="3">
+      <ns0:c r="A3" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>역할</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B3" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>스킬 입력과 해금 처리가 읽는다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C3" s="1" t="n"/>
+      <ns0:c r="D3" s="1" t="n"/>
+      <ns0:c r="E3" s="1" t="n"/>
+      <ns0:c r="F3" s="1" t="n"/>
+      <ns0:c r="G3" s="1" t="n"/>
+      <ns0:c r="H3" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="A4" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>의도</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B4" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>무기마다 스킬을 붙이기 위해.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C4" s="1" t="n"/>
+      <ns0:c r="D4" s="1" t="n"/>
+      <ns0:c r="E4" s="1" t="n"/>
+      <ns0:c r="F4" s="1" t="n"/>
+      <ns0:c r="G4" s="1" t="n"/>
+      <ns0:c r="H4" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="A5" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>비고</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B5" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Name, Note</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C5" s="1" t="n"/>
+      <ns0:c r="D5" s="1" t="n"/>
+      <ns0:c r="E5" s="1" t="n"/>
+      <ns0:c r="F5" s="1" t="n"/>
+      <ns0:c r="G5" s="1" t="n"/>
+      <ns0:c r="H5" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="A6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Name</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>TextID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>WeaponID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>StateID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>DamageMult</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PoiseDamage</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Cooldown</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>UnlockType</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Effect</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Note</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="A7" s="3" t="n">
+        <ns0:v>7001</ns0:v>
+      </ns0:c>
+      <ns0:c r="B7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>결박 가르기</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C7" s="3" t="n">
+        <ns0:v>30010</ns0:v>
+      </ns0:c>
+      <ns0:c r="D7" s="3" t="n">
+        <ns0:v>6002</ns0:v>
+      </ns0:c>
+      <ns0:c r="E7" s="3" t="n">
+        <ns0:v>10009</ns0:v>
+      </ns0:c>
+      <ns0:c r="F7" s="3" t="n">
+        <ns0:v>15000</ns0:v>
+      </ns0:c>
+      <ns0:c r="G7" s="3" t="n">
+        <ns0:v>30</ns0:v>
+      </ns0:c>
+      <ns0:c r="H7" s="3" t="n">
+        <ns0:v>8000</ns0:v>
+      </ns0:c>
+      <ns0:c r="I7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ROOM_LEDGER</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CUT_BIND</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장부방에서 해금, 결박 문·사슬 끊기</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</ns0:worksheet>
 </file>
--- a/tables/Skill.xlsx
+++ b/tables/Skill.xlsx
@@ -435,227 +435,227 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:sheetPr>
-    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
-    <ns0:pageSetUpPr/>
-  </ns0:sheetPr>
-  <ns0:dimension ref="A1:K7"/>
-  <ns0:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <ns0:cols>
-    <ns0:col width="7.25" customWidth="1" min="1" max="1"/>
-    <ns0:col width="7.88" customWidth="1" min="2" max="2"/>
-    <ns0:col width="8.380000000000001" customWidth="1" min="3" max="3"/>
-    <ns0:col width="9.380000000000001" customWidth="1" min="4" max="4"/>
-    <ns0:col width="8.25" customWidth="1" min="5" max="5"/>
-    <ns0:col width="12.25" customWidth="1" min="6" max="6"/>
-    <ns0:col width="8.380000000000001" customWidth="1" min="7" max="7"/>
-    <ns0:col width="12.25" customWidth="1" min="8" max="8"/>
-    <ns0:col width="8.380000000000001" customWidth="1" min="9" max="9"/>
-    <ns0:col width="30.38" customWidth="1" min="10" max="10"/>
-  </ns0:cols>
-  <ns0:sheetData>
-    <ns0:row r="1">
-      <ns0:c r="A1" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>규칙</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B1" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">한 행 = 스킬 하나. MP 없음, Cooldown(ms)만. WeaponID는 Item ID, StateID는 State ID. DamageMult는 만분율(10000 = ATK 그대로), PoiseDamage는 체세 피해. 스킬 공격은 회피 불가(옛 Attack 5006 값을 옮김, 10/29).
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7.25" customWidth="1" min="1" max="1"/>
+    <col width="7.88" customWidth="1" min="2" max="2"/>
+    <col width="8.380000000000001" customWidth="1" min="3" max="3"/>
+    <col width="9.380000000000001" customWidth="1" min="4" max="4"/>
+    <col width="8.25" customWidth="1" min="5" max="5"/>
+    <col width="12.25" customWidth="1" min="6" max="6"/>
+    <col width="8.380000000000001" customWidth="1" min="7" max="7"/>
+    <col width="12.25" customWidth="1" min="8" max="8"/>
+    <col width="8.380000000000001" customWidth="1" min="9" max="9"/>
+    <col width="30.38" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>한 행 = 스킬 하나. MP 없음, Cooldown(ms)만. WeaponID는 Item ID, StateID는 State ID. Damage는 TotalATK에 더하는 정수 추가 데미지(10/29 더하기 방식, 옛 DamageMult), PoiseDamage는 체세 피해. 스킬 공격은 회피 불가(옛 Attack 5006 값을 옮김, 10/29).
 [추출 지정 규칙]
 @column Name=TextID;Type=Integer;Minimum=1;ReferenceTable=Language
 @column Name=WeaponID;Type=Integer;Minimum=1;ReferenceTable=Item
 @column Name=StateID;Type=Integer;Minimum=0;ReferenceTable=State
-@column Name=DamageMult;Type=Integer;Minimum=0;Unit=per_10000
+@column Name=Damage;Type=Integer;Minimum=0
 @column Name=PoiseDamage;Type=Integer;Minimum=0
 @column Name=Cooldown;Type=Integer;Minimum=0;Unit=ms
 @column Name=UnlockType;Type=Text;AllowedValues=ROOM_LEDGER
 @column Name=Effect;Type=Text;AllowedValues=CUT_BIND
-@check Kind=ReferenceValue;Column=WeaponID;Table=Item;TargetColumn=ItemType;Value=Weapon;Code=ITEM_TYPE</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C1" s="1" t="n"/>
-      <ns0:c r="D1" s="1" t="n"/>
-      <ns0:c r="E1" s="1" t="n"/>
-      <ns0:c r="F1" s="1" t="n"/>
-      <ns0:c r="G1" s="1" t="n"/>
-      <ns0:c r="H1" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="2">
-      <ns0:c r="A2" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>기능</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B2" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>CSV,스킬 공격·쿨타임·해금 방식·효과.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C2" s="1" t="n"/>
-      <ns0:c r="D2" s="1" t="n"/>
-      <ns0:c r="E2" s="1" t="n"/>
-      <ns0:c r="F2" s="1" t="n"/>
-      <ns0:c r="G2" s="1" t="n"/>
-      <ns0:c r="H2" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="3">
-      <ns0:c r="A3" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>역할</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B3" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>스킬 입력과 해금 처리가 읽는다.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C3" s="1" t="n"/>
-      <ns0:c r="D3" s="1" t="n"/>
-      <ns0:c r="E3" s="1" t="n"/>
-      <ns0:c r="F3" s="1" t="n"/>
-      <ns0:c r="G3" s="1" t="n"/>
-      <ns0:c r="H3" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="4">
-      <ns0:c r="A4" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>의도</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B4" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>무기마다 스킬을 붙이기 위해.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C4" s="1" t="n"/>
-      <ns0:c r="D4" s="1" t="n"/>
-      <ns0:c r="E4" s="1" t="n"/>
-      <ns0:c r="F4" s="1" t="n"/>
-      <ns0:c r="G4" s="1" t="n"/>
-      <ns0:c r="H4" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="5">
-      <ns0:c r="A5" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>비고</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B5" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Name, Note</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C5" s="1" t="n"/>
-      <ns0:c r="D5" s="1" t="n"/>
-      <ns0:c r="E5" s="1" t="n"/>
-      <ns0:c r="F5" s="1" t="n"/>
-      <ns0:c r="G5" s="1" t="n"/>
-      <ns0:c r="H5" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="6">
-      <ns0:c r="A6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>ID</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Name</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>TextID</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>WeaponID</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>StateID</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>DamageMult</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="G6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>PoiseDamage</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Cooldown</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>UnlockType</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="J6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Effect</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="K6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Note</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="7">
-      <ns0:c r="A7" s="3" t="n">
-        <ns0:v>7001</ns0:v>
-      </ns0:c>
-      <ns0:c r="B7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>결박 가르기</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C7" s="3" t="n">
-        <ns0:v>30010</ns0:v>
-      </ns0:c>
-      <ns0:c r="D7" s="3" t="n">
-        <ns0:v>6002</ns0:v>
-      </ns0:c>
-      <ns0:c r="E7" s="3" t="n">
-        <ns0:v>10009</ns0:v>
-      </ns0:c>
-      <ns0:c r="F7" s="3" t="n">
-        <ns0:v>15000</ns0:v>
-      </ns0:c>
-      <ns0:c r="G7" s="3" t="n">
-        <ns0:v>30</ns0:v>
-      </ns0:c>
-      <ns0:c r="H7" s="3" t="n">
-        <ns0:v>8000</ns0:v>
-      </ns0:c>
-      <ns0:c r="I7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>ROOM_LEDGER</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="J7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>CUT_BIND</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="K7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>장부방에서 해금, 결박 문·사슬 끊기</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-  </ns0:sheetData>
-  <ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</ns0:worksheet>
+@check Kind=ReferenceValue;Column=WeaponID;Table=Item;TargetColumn=ItemType;Value=Weapon;Code=ITEM_TYPE</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>CSV,스킬 공격·쿨타임·해금 방식·효과.</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>스킬 입력과 해금 처리가 읽는다.</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>의도</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>무기마다 스킬을 붙이기 위해.</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="1" t="n"/>
+      <c r="F4" s="1" t="n"/>
+      <c r="G4" s="1" t="n"/>
+      <c r="H4" s="1" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Name, Note</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+      <c r="E5" s="1" t="n"/>
+      <c r="F5" s="1" t="n"/>
+      <c r="G5" s="1" t="n"/>
+      <c r="H5" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>TextID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>WeaponID</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>StateID</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>PoiseDamage</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>UnlockType</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>7001</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>결박 가르기</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>30010</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>6002</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>10009</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>ROOM_LEDGER</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>CUT_BIND</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>장부방에서 해금, 결박 문·사슬 끊기</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>